--- a/src/main/resources/templates/system/export/simple.xlsx
+++ b/src/main/resources/templates/system/export/simple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\HM\JAVA\DM\nitsm\src\main\resources\templates\system\export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tool\DM\nitsm_jinan\src\main\resources\templates\system\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4509453A-5D7C-49CC-9B73-52DFBB4B4172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513ED127-535C-4613-B071-08BF9629DA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -697,26 +697,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations xWindow="1174" yWindow="448" count="20">
+  <dataValidations xWindow="1174" yWindow="448" count="12">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="终端可为空" prompt=" " sqref="G1" xr:uid="{C9199D6D-342C-4063-A819-A170AEE39906}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="除终端设备外,皆需填写机柜及位置信息" sqref="G3:G5" xr:uid="{F9CBDB85-3314-4E66-B05B-1D773C5A0C8D}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="终端可为空" prompt="0~42" sqref="H1:I1" xr:uid="{A946CC27-1FDD-4641-B07F-724F66573938}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请填写:整数0~42" sqref="H3:I5" xr:uid="{B3BF3DC5-1F9F-4FA1-B33A-F60791A6F14F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="安全边界/PDU等类型无需填写ip地址" prompt=" " sqref="J1" xr:uid="{E9FF10D0-E8E9-4455-AC8A-2136CF0AE41C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="安全边界/PDU等类型无需填写ip" sqref="J3:J5" xr:uid="{8DD76370-C485-4455-A707-948417357905}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="*必填" prompt=" " sqref="A1:F1" xr:uid="{D8D135C1-6086-4EC7-8E45-34160A7A85A5}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="必填" prompt=" " sqref="K1" xr:uid="{B4EDE4FD-F779-4330-9502-8E386B0056A7}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="必填" sqref="K3:K5 A3:F3 A5:F5 A4 C4:F4" xr:uid="{5A62C7E7-BCAC-4B1C-A809-8CF21E1B596B}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="是否为需要监控设备(会验证采集相关信息)" prompt=" " sqref="L1" xr:uid="{52ACE6EB-96D8-42B5-AE9B-981433FFC031}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="是否需要在前台topo图上显示" prompt=" " sqref="M1" xr:uid="{2AA0C85B-1297-43BB-B0BC-917DFC604347}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可空" prompt="默认为否" sqref="L3:M5" xr:uid="{4C64CA98-A193-49C0-AFA6-22516186B456}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="监控服务器/工控机/终端时 :需填写" prompt="不监控时无需填写" sqref="O1" xr:uid="{886B208A-0092-4029-9F2A-722ADD4E41D9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="linux/windows/aix" prompt=" 不监控无需填写" sqref="O3:O5" xr:uid="{C9C8112F-13B2-4428-89E6-3FF0C3C09098}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="采集类型&gt;windows(填团体名称)_x000a_其余采集类型&gt;(用户名+密码)" sqref="P1" xr:uid="{0E2C790B-680D-42E0-AFC5-5282F21C9527}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控无需填写" prompt="小型机-&gt;用户名密码_x000a_交换机/路由器-&gt;团体名" sqref="P3:P5" xr:uid="{EF2BE46A-1F07-4D9E-AFB4-45A0481EEB14}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="服务器/工控机/终端" prompt="以上设备:windows采集类型时,需填写登录密码" sqref="Q2:Q5" xr:uid="{4109E7AE-E929-45A3-8193-497FF5E0B310}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="服务器/工控机/终端" prompt="以上设备:windows采集类型时,需填写登录密码" sqref="Q2" xr:uid="{4109E7AE-E929-45A3-8193-497FF5E0B310}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="交换机/路由器" prompt="如需设置为核心交换机或核心路由器可填写" sqref="N1" xr:uid="{DC11F3C3-979D-40F5-8030-D0EB097E3E59}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="可空" prompt="默认为普通网络设备" sqref="N3:N5" xr:uid="{2538B52D-F55F-45E8-9A09-3B98A6DF5657}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="不监控时无需填写" prompt="服务器/工控机/终端_x000a_以上设备:windows采集类型时,需填写登录密码" sqref="Q1" xr:uid="{B5A5F943-A569-473C-952B-7D5EBEB4097E}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
